--- a/data/processed/document_metadata.xlsx
+++ b/data/processed/document_metadata.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-2200-08-05</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-08-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -480,14 +480,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Coarse Ore Stockpile 2 Conveyor Motor M21 &amp; M22 2200-08-05</t>
+          <t>Mechanical HOP of Rougher 1st Concentrate Hopper 1 3310-08-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-2200-08-05</t>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-08-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,14 +497,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 2200-08-05 Coarse Ore Stockpile Conveyor Motor M21 &amp; M22</t>
+          <t>Piping HOP of Rougher 1st Concentrate Hopper 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-2200-08-05</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-08-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -514,14 +514,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 2200-08-05 Coarse Ore Stockpile Conveyor Motor M21 &amp; M22</t>
+          <t>Instrument HOP of Subsystem 3310-08-01 Rougher 1st Concentrate Hopper 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-3310-09-03</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-09-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Rougher 2nd Concentrate Hopper 1 Pump 2 3310-09-03</t>
+          <t>Mechanical HOP of Rougher 2nd Concentrate Hopper 1 3310-09-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-09-03</t>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -548,14 +548,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Piping HOP of Rougher 2nd Concentrate Hopper 1 Pump 2 &amp; VSD</t>
+          <t>Piping HOP of Rougher 2nd Concentrate Hopper 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-3310-09-03</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -565,14 +565,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 3310-09-03 Rougher 2nd Concentrate Hopper 1 Pump 2 &amp; VSD</t>
+          <t>Instrument HOP of Subsystem 3310-09-01 Rougher 2nd Concentrate Hopper 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-3310-09-03</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-17-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -582,14 +582,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 3310-09-03 Rougher 2nd Concentrate Hopper 1 Pump 2 &amp; VSD</t>
+          <t>Mechanical HOP of Rougher 1st Concentrate Hopper 2 Pump 2 3310-17-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-3410-13-04</t>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-17-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,14 +599,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Subsystem 3410-13-04 1st Sulfide Cleaner 2 Cell 3 3412-FC-042 3412-FC-042-M01</t>
+          <t>Piping HOP of Rougher 1st Concentrate Hopper 2 Pump 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-50-HOP-FT-3410-13-04</t>
+          <t>PR2ME-PIL-QTY-65-HOP-3310-17-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -616,14 +616,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piping HOP of 1st Sulfide Cleaner 2 Cell 3</t>
+          <t>Electrical HOP of Subsystem 3310-17-03 Rougher 1st Concentrate Hopper 2 Pump 2 &amp; VSD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-3410-13-04</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-17-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -633,14 +633,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 3410-13-04 1st Sulfide Cleaner 2 Cell 3</t>
+          <t>Instrument HOP of Subsystem 3310-17-03 Rougher 1st Concentrate Hopper 2 Pump 2 &amp; VSD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-3410-13-04</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3510-01-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -650,14 +650,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 3410-13-04 1st Sulfide Cleaner 2 Cell 3</t>
+          <t>Mechanical HOP of CCD Thickener Area Sump Pump 1 3510-01-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-50-HOP-HO-3120-01-06</t>
+          <t>PR2ME-PIL-QTY-50-HOP-SP-3510-01-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,14 +667,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Piping HOP of Ball Mill 6 Hydraulic Brake System</t>
+          <t>Piping HOP of CCD Thickener Area Sump Pump 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PR2ME-3194-PIL-QTY-65-HOP-0003</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-01-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -684,14 +684,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 3194-50-08/09/11/13/14-3120-01-04/06/07/08-L&amp;SP Distribution Board, Ball Mill 6 LV MCCs/6.6kVSwitchboard/Substation/Ball Mill 6 Gearless Ring Motor &amp; Hydraulic Brake System &amp; Bearing Lube System&amp; Main Bearing Seal Grease System</t>
+          <t>Instrument HOP of Subsystem 3510-01-01 CCD Thickener Area Sump Pump 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-3120-01-07</t>
+          <t>PR2ME-PIL-QTY-65-HOP-3510-01-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -701,14 +701,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Ball Mill 6 Bearing Lube System 3123-FA-452</t>
+          <t>Electrical HOP of Subsystem 3510-01-01  CCD Thickener Area Sump Pump 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-50-HOP-LOH-3120-01-07</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3510-04-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -718,14 +718,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Piping HOP of Ball Mill 6 Bearing Lube System</t>
+          <t>Mechanical HOP of CCD Thickener 6  Feed Box 3510-04-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-3120-01-07</t>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3510-04-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 3120-01-07 Ball Mill 6 Bearing Lube System</t>
+          <t>Piping HOP of CCD Thickener 6 Feed Box</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-2120-02-03</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-04-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -752,14 +752,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Surge Pile 2 Apron Feeder 1 &amp; VSD &amp; Cooling System &amp; Feed Hopper 2120-02-03</t>
+          <t>Instrument HOP of Subsystem 3510-04-01 CCD Thickener 6 Feed Box</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-2120-02-03</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3530-01-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -769,14 +769,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 2120-02-03 Surge Pile 2 Apron Feeder 1 &amp; VSD &amp; Cooling System &amp; Feed Hoppers</t>
+          <t>Mechanical HOP of Concentrate Storage  Distribution Box 3530-01-04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-2120-02-03</t>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3530-01-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -786,14 +786,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 2120-02-03 Surge Pile 2 Apron Feeder 1 &amp; VSD &amp; Cooling System &amp; Feed Hoppers</t>
+          <t>Piping HOP of Concentrate Storage Distribution Box</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-2110-13-02</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3530-01-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -803,14 +803,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Primary Crusher 4 Discharge Conveyor Weightometer 2110-13-02</t>
+          <t>Instrument HOP of Subsystem 3530-01-04 Concentrate Storage Distribution Box</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-2110-13-02</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-06-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -820,14 +820,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 2110-13-02 Primary Crusher 4 Discharge Conveyor Weightometer</t>
+          <t>Mechanical HOP of Subsystem 3410-06-02 3411-PU-173 Coarse Cleaner Tails Pump 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-2110-13-01</t>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3410-06-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -837,14 +837,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Primary Crusher 4 Discharge Conveyor 2110-13-01</t>
+          <t>Piping HOP of Coarse Cleaner Tails Pump 1 VSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-2110-13-01</t>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-06-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -854,14 +854,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 2110-13-01 Primary Crusher 4 Discharge Conveyor</t>
+          <t>Electrical HOP of Subsystem 3410-06-04 Rougher Flotation Area Sump Pumps 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-2110-01-04</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-06-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -871,14 +871,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Primary Crusher 3 Spider Lube Oil System 2110-01-04</t>
+          <t>Instrument HOP of Subsystem 3410-06-02 Coarse Cleaner Tails Pump 1 VSD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-2110-01-04</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3420-15-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -888,14 +888,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 2110-01-04 Primary Crusher 3 Spider Lube oil System</t>
+          <t>Mechanical HOP of Subsystem 3420-15-02 3422-FC-072 3rd Oxide Cleaner Cell 2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-2110-01-04</t>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3420-15-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -905,14 +905,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 2110-01-04 Primary crusher 3 Spider Lube Oil System</t>
+          <t>Piping HOP of 3rd Oxide Cleaner Cell 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-3580-08-05</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3420-15-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -922,14 +922,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Grinding Lime Ringmain Pump 2 3188-PU-082</t>
+          <t>Instrument HOP of Subsystem 3420-15-02 1st Sulfide Cleaner Standby Feed Pump VSD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-50-HOP-ML-3580-08-05</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3120-02-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Piping HOP of Grinding Lime Ringmain Pump 2</t>
+          <t>Mechanical HOP of Line 4 Cyclone Feed Hopper 3122-CH-406 HO-404</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-3580-08-05</t>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3120-02-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -956,14 +956,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 3580-08-05 Grinding Lime Ringmain Pump 2</t>
+          <t>Piping HOP of Ball Mill 6 Cooling Water</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-3580-08-05</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3120-02-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -973,14 +973,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 3580-08-05 Grinding Lime Ringmain Pump 2</t>
+          <t>Instrument HOP of Subsystem 3120-02-01 Line 4 Cyclone Feed Hopper</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-2193-50-08</t>
+          <t>PR2ME-PIL-QTY-59-HOP-3110-02-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -990,14 +990,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 2193-50-08 2193-DB-002/2123-DB-001/2193-DB-003/L&amp;SP Distribution Board</t>
+          <t>Mechanical HOP of Line 3 Cyclone Cluster 5 Feed Pump &amp; VSD &amp; Horizontal &amp; Vertical Bends 3112-ME-303 3112-ME-304 3113-PU-351</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-2291-50-10</t>
+          <t>PR2ME-PIL-QTY-50-HOP-CY-3110-02-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1007,14 +1007,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 2291-50-10 2210-WO-001/2310-WO-001 Welding Outlet</t>
+          <t>Piping HOP of Line 3 Cyclone Cluster 5 Feed Pump &amp; VSD &amp; Horizontal &amp; Vertical Bends</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-3194-90-01</t>
+          <t>PR2ME-PIL-QTY-65-HOP-3110-02-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1024,7 +1024,687 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Instrument (PCS) HOP of Subsystem 3194-90-01 Ball Mill  6 CCTV</t>
+          <t>Electrical HOP of Subsystem 3110-02-03 Line 3 Cyclone Cluster 5 Feed Pump &amp; VSD &amp; Horizontal &amp; Vertical Bends</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3110-02-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3110-02-03 Line 3 Cyclone Cluster 5 Feed Pump</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen 2320-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-SP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Piping HOP of Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2320-01-02 Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2320-01-02 Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-01-04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 4 SAG Mill New &amp; Total Feed Conveyor Weightometers 2320-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2320-01-04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2320-01-04 Line 4 SAG Mill New &amp; Total Feed Conveyor Weightometers</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-02-05</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 3 SAG Mill Conveyor Motor 2320-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2320-02-05</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2320-02-05 Line 3 SAG Mill Conveyor Motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-05-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2310-05-02 2311-FE-401 Image Analyzing System</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-06-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2310-06-02 2311-FE-402 Image Analyzing System</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-07-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2310-07-02 2311-FE-403 Image Analyzing System</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-01-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of OLC 2 Transfer Area Fire Water Tank 2120-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FW-2120-01-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Piping HOP of OLC 2 Transfer Area Fire Water Tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2120-01-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2120-01-02 OLC 2 Transfer Area Fire Water Tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-01-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Fire Water Pumps Package Vendor Package 2120-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FW-2120-01-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Piping HOP of Fire Water Pumps Package Vendor Package</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2120-01-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2120-01-01 Fire Water Pumps</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2110-90-09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Primary Crusher 3&amp;4 Discharge Conveyor Head Pulley Replacement Hoist 2110-90-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2110-90-09</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2110-90-09 Primary Crusher 3 &amp; 4 Discharge Conveyor Head Pulley Replacement Hoist</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2100-01-01/02/03 Primary Crusher 3 Discharge Chute Air Cannon 1/2/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2100-01-02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Primary Crusher 3 Discharge Chute Air Cannon 2 2100-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-02-04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of CCD 6 Flocculant Mixer 3580-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FL-3580-02-04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Piping HOP of CCD 6 Flocculant Mixer</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-02-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-02-04 CCD 6 Flocculant Mixer</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Lime Transfer Pumps 1 3580-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-ML-3580-07-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Piping HOP of Lime Transfer Pump 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-07-01 Lime Transfer Pump 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-07-01 Lime Transfer Pump 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3580-08-04 Grinding Lime Ringmain Pump 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-GWP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Piping HOP of Grinding Lime Ringmain Pump 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-08-04 Grinding Lime Ring main Pump 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-08-04 Grinding Lime Ringmain Pump 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Primary Crusher 3 Discharge Chute Air Cannon 1 2100-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-AP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Piping HOP of Primary Crusher 3 Discharge Chute Air Cannon 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2191-50-09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2191-50-09 2111-WO-001 Welding Outlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2114-90-01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 2114-90-01 Camera-Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3191-90-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 3191-90-01 Camera-Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3193-90-01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 3193-90-01 Camera-Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3591-90-01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 3591-90-01 Camera-Network</t>
         </is>
       </c>
     </row>

--- a/data/processed/document_metadata.xlsx
+++ b/data/processed/document_metadata.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-2110-01-01</t>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-90-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -480,14 +480,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Primary Crusher 3 2110-01-01</t>
+          <t>Mechanical HOP of Surge Pile 2 Maintenance Trolleys 2120-90-09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-2110-01-01</t>
+          <t>PR2ME-PIL-QTY-65-HOP-2120-90-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,14 +497,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 2110-01-01 Primary Crusher 3</t>
+          <t>Electrical HOP of Subsystem 2120-90-09 Surge Pile 2 Maintenance Trolleys</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-70-HOP-2110-01-01</t>
+          <t>PR2ME-PIL-QTY-50-HOP-KC-3160-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -514,14 +514,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Instrument HOP of Subsystem 2110-01-01 Primary Crusher 3</t>
+          <t>Piping HOP of SAG Mill 4 Cooling Water</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-59-HOP-4130-90-01</t>
+          <t>PR2ME-PIL-QTY-70-HOP-3160-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mechanical HOP of Concentrate Pump Station Maintenance Hoist 4130-90-01</t>
+          <t>Instrument HOP of Subsystem 3160-03-02 SAG Mill 4 Cooling Water</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PR2ME-PIL-QTY-65-HOP-4130-90-01</t>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3510-03-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -548,7 +548,330 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Electrical HOP of Subsystem 4130-90-01 Concentrate Pump Station Maintenance Hoist</t>
+          <t>Piping HOP of CCD Thickener 5 Underflow Pump 1 &amp; 2 To Feed Boxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-03-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3510-03-06 CCD Thickener 5 Underflow Pumps 1 &amp; 2 to Feed Boxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3420-13-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3420-13-02 3422-FC-067 3422-FC-067-M01 2nd Oxide Cleaner Cell 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FT-3420-13-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Piping HOP of 2nd Oxide Cleaner Cell 2 &amp; Agitator</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3420-13-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3420-13-02 2nd Oxide Cleaner Cell 2 &amp; Agitator</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3420-13-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3420-13-02 2nd Oxide Cleaner Cell 2 &amp; Agitator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3140-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3140-01-01 3141-CV-007, 3141-BS-007, 3141-BS-008, 3141-BS-010, 3141-CH-009 SAG Mill Pebble Screen Oversize Conveyor 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3140-01-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3140-01-01 SAG Mill Pebble Screen Oversize Conveyor 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3140-01-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3140-01-01 SAG Mill Pebble Screen Oversize Conveyor 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3220-07-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3220-07-02 3223-SC-404 Ball Mill 6 Crushed Pebble Conveyor Weightometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3220-07-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3220-07-02 Ball Mill 6 Crushed Pebble Conveyor Weightometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-05-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Lime Slacking Mill 1 Cyclone Feed Pump 1 &amp; VSD 3580-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-GWF-3580-05-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Piping HOP of Lime Slacking Mill 1 Cyclone Feed Pump 1 &amp; VSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-05-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-05-01 Lime Slaking Mill 1 Cyclone Feed Pump 1 &amp; VSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-05-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-05-01 Lime Slaking Mill 1 Cyclone Feed Pump 1 &amp; VSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-07-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Lime Transfer Pumps 3 3580-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-ML-3580-07-03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Piping HOP of Lime Transfer Pump 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-07-03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-07-03 Lime Transfer Pump 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-07-03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-07-03 Lime Transfer Pump 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2191-90-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 2191-90-01 Camera-Network</t>
         </is>
       </c>
     </row>
